--- a/data/all_species_20250330.xlsx
+++ b/data/all_species_20250330.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10309"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pranavgokhale/GaTech Dropbox/Pranav Gokhale/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/08a8e39d01a05c2a/Documents/02_personal/04_education/01_GT_MS/01_courses/2025/haag research/bird_audio_2025/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A065ACF-AB06-E741-A6DB-D4D3898CDDDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{7A065ACF-AB06-E741-A6DB-D4D3898CDDDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{698CD8B9-8A0E-4DD5-AD97-B41EEBEDFFDD}"/>
   <bookViews>
-    <workbookView xWindow="260" yWindow="1500" windowWidth="27640" windowHeight="16940" xr2:uid="{8F16C950-D97C-A64B-8131-10EEB12618CB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{8F16C950-D97C-A64B-8131-10EEB12618CB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -176,9 +176,6 @@
     <t>Western Yellow Wagtail</t>
   </si>
   <si>
-    <t>Pale Martin??</t>
-  </si>
-  <si>
     <t>Russet Sparrow</t>
   </si>
   <si>
@@ -444,6 +441,9 @@
   </si>
   <si>
     <t>Luscinia phaenicuroides</t>
+  </si>
+  <si>
+    <t>Pale Martin</t>
   </si>
 </sst>
 </file>
@@ -823,23 +823,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{455C34BF-059D-6948-B883-E17B80943B01}">
   <dimension ref="A1:C68"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.19921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.796875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="10.83203125" style="1"/>
+    <col min="4" max="16384" width="10.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.15">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -847,10 +847,10 @@
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.15">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -858,10 +858,10 @@
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.15">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -869,10 +869,10 @@
         <v>3</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.15">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -880,10 +880,10 @@
         <v>4</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.15">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -891,10 +891,10 @@
         <v>5</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.15">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -902,10 +902,10 @@
         <v>6</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.15">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -913,10 +913,10 @@
         <v>7</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.15">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -924,10 +924,10 @@
         <v>8</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.15">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -935,10 +935,10 @@
         <v>9</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.15">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -946,10 +946,10 @@
         <v>10</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.15">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -957,10 +957,10 @@
         <v>11</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.15">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -968,10 +968,10 @@
         <v>12</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.15">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -979,10 +979,10 @@
         <v>13</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.15">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -990,10 +990,10 @@
         <v>14</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.15">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -1001,10 +1001,10 @@
         <v>15</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.15">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -1012,10 +1012,10 @@
         <v>16</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.15">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -1023,10 +1023,10 @@
         <v>17</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.15">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -1034,10 +1034,10 @@
         <v>18</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.15">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -1045,10 +1045,10 @@
         <v>19</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.15">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -1056,10 +1056,10 @@
         <v>20</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.15">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -1067,10 +1067,10 @@
         <v>21</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.15">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -1078,32 +1078,32 @@
         <v>22</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.15">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.15">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.15">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -1111,10 +1111,10 @@
         <v>23</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.15">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -1122,10 +1122,10 @@
         <v>24</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.15">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -1133,10 +1133,10 @@
         <v>25</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.15">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -1144,10 +1144,10 @@
         <v>26</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.15">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -1155,10 +1155,10 @@
         <v>27</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.15">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -1166,10 +1166,10 @@
         <v>28</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.15">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -1177,65 +1177,65 @@
         <v>29</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.15">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.15">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.15">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.15">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.15">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.15">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -1243,32 +1243,32 @@
         <v>30</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.15">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.15">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.15">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -1276,21 +1276,21 @@
         <v>31</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.15">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>41</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.15">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -1298,65 +1298,65 @@
         <v>32</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.15">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>43</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.15">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>44</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.15">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>45</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.15">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>46</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.15">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>47</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.15">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>48</v>
       </c>
@@ -1364,10 +1364,10 @@
         <v>33</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.15">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>49</v>
       </c>
@@ -1375,21 +1375,21 @@
         <v>34</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.15">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>50</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.15">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>51</v>
       </c>
@@ -1397,43 +1397,43 @@
         <v>35</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.15">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>52</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.15">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>53</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.15">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>54</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.15">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>55</v>
       </c>
@@ -1441,10 +1441,10 @@
         <v>36</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.15">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>56</v>
       </c>
@@ -1452,10 +1452,10 @@
         <v>37</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.15">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>57</v>
       </c>
@@ -1463,10 +1463,10 @@
         <v>38</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.15">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>58</v>
       </c>
@@ -1474,10 +1474,10 @@
         <v>39</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.15">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>59</v>
       </c>
@@ -1485,10 +1485,10 @@
         <v>40</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.15">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>60</v>
       </c>
@@ -1496,10 +1496,10 @@
         <v>41</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.15">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>61</v>
       </c>
@@ -1507,10 +1507,10 @@
         <v>42</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.15">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>62</v>
       </c>
@@ -1518,10 +1518,10 @@
         <v>43</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.15">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>63</v>
       </c>
@@ -1529,10 +1529,10 @@
         <v>44</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.15">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>64</v>
       </c>
@@ -1540,40 +1540,40 @@
         <v>45</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.15">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>65</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>46</v>
+        <v>135</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.15">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>66</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.15">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>67</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
